--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ILLINOIS_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ILLINOIS_2020.xlsx
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C108">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C130">
@@ -3379,7 +3379,7 @@
         <v>41</v>
       </c>
       <c r="D168">
-        <v>0.0009750297265160523</v>
+        <v>0.0009750297265160524</v>
       </c>
     </row>
     <row r="169">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C179">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C209">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C276">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C312">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C323">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C333">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C429">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C494">
@@ -10021,7 +10021,7 @@
         <v>41</v>
       </c>
       <c r="D537">
-        <v>0.0009750297265160523</v>
+        <v>0.0009750297265160524</v>
       </c>
     </row>
     <row r="538">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C614">
@@ -11677,7 +11677,7 @@
         <v>41</v>
       </c>
       <c r="D629">
-        <v>0.0009750297265160523</v>
+        <v>0.0009750297265160524</v>
       </c>
     </row>
     <row r="630">
@@ -12613,7 +12613,7 @@
         <v>41</v>
       </c>
       <c r="D681">
-        <v>0.0009750297265160523</v>
+        <v>0.0009750297265160524</v>
       </c>
     </row>
     <row r="682">
@@ -14413,7 +14413,7 @@
         <v>38</v>
       </c>
       <c r="D781">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="782">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C795">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C796">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C820">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C849">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C908">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C956">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C963">
@@ -18715,7 +18715,7 @@
         <v>38</v>
       </c>
       <c r="D1020">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1021">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C1071">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C1117">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C1207">
@@ -22855,7 +22855,7 @@
         <v>38</v>
       </c>
       <c r="D1250">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1251">
@@ -23593,7 +23593,7 @@
         <v>38</v>
       </c>
       <c r="D1291">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1292">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C1339">
@@ -24709,7 +24709,7 @@
         <v>38</v>
       </c>
       <c r="D1353">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1354">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C1360">
@@ -26257,7 +26257,7 @@
         <v>38</v>
       </c>
       <c r="D1439">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1440">
@@ -27265,7 +27265,7 @@
         <v>38</v>
       </c>
       <c r="D1495">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1496">
@@ -29191,7 +29191,7 @@
         <v>38</v>
       </c>
       <c r="D1602">
-        <v>0.0009036860879904875</v>
+        <v>0.0009036860879904876</v>
       </c>
     </row>
     <row r="1603">
